--- a/data/trans_bre/P6902-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 40,41</t>
+          <t>3,47; 42,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 36,06</t>
+          <t>-4,12; 37,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 26,92</t>
+          <t>-17,53; 27,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 31,43</t>
+          <t>-2,07; 31,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 287,06</t>
+          <t>7,3; 298,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 122,73</t>
+          <t>-9,55; 129,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 88,51</t>
+          <t>-36,75; 84,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 91,61</t>
+          <t>-3,6; 94,33</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 19,32</t>
+          <t>-13,08; 18,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 23,09</t>
+          <t>-11,45; 22,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 27,51</t>
+          <t>-7,61; 27,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 22,06</t>
+          <t>-3,14; 23,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 51,76</t>
+          <t>-27,82; 46,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 54,08</t>
+          <t>-19,18; 53,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 75,35</t>
+          <t>-15,33; 74,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 48,45</t>
+          <t>-5,06; 50,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 39,85</t>
+          <t>4,62; 40,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 20,35</t>
+          <t>-15,48; 21,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 46,21</t>
+          <t>16,51; 46,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 12,0</t>
+          <t>-55,97; 10,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 109,31</t>
+          <t>9,84; 110,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 44,82</t>
+          <t>-26,36; 49,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,18; 174,52</t>
+          <t>40,05; 182,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,17; 18,96</t>
+          <t>-71,81; 17,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 8,13</t>
+          <t>-19,69; 6,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 30,76</t>
+          <t>-4,07; 30,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 25,5</t>
+          <t>-5,31; 26,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 1,38</t>
+          <t>-24,65; 0,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 15,32</t>
+          <t>-31,78; 13,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 79,35</t>
+          <t>-8,14; 75,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 50,42</t>
+          <t>-7,98; 52,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 1,5</t>
+          <t>-29,73; 0,51</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 17,13</t>
+          <t>-0,27; 15,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 19,07</t>
+          <t>2,11; 19,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 26,25</t>
+          <t>9,03; 26,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 8,58</t>
+          <t>-19,44; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 43,04</t>
+          <t>-0,43; 39,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 44,65</t>
+          <t>4,33; 45,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 65,36</t>
+          <t>19,68; 65,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 14,38</t>
+          <t>-30,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6902-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,27</t>
+          <t>16,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 42,65</t>
+          <t>3,77; 42,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 37,05</t>
+          <t>-3,05; 38,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 27,87</t>
+          <t>-19,79; 25,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 31,21</t>
+          <t>0,15; 32,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 298,94</t>
+          <t>10,04; 321,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 129,4</t>
+          <t>-11,8; 127,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 84,3</t>
+          <t>-39,42; 76,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 94,33</t>
+          <t>-0,59; 93,54</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,01</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 18,25</t>
+          <t>-14,66; 16,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 22,39</t>
+          <t>-9,93; 21,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 27,35</t>
+          <t>-7,94; 26,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 23,06</t>
+          <t>-5,81; 19,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 46,58</t>
+          <t>-31,03; 41,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 53,88</t>
+          <t>-18,71; 50,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 74,66</t>
+          <t>-16,21; 74,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 50,49</t>
+          <t>-9,52; 37,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,89</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-28,58%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 40,57</t>
+          <t>4,58; 38,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 21,75</t>
+          <t>-14,25; 21,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 46,37</t>
+          <t>17,31; 46,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 10,86</t>
+          <t>-5,78; 26,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 110,57</t>
+          <t>8,51; 110,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 49,76</t>
+          <t>-23,98; 50,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,05; 182,53</t>
+          <t>44,45; 178,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 17,86</t>
+          <t>-7,82; 58,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,51</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-13,03%</t>
+          <t>-7,65%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 6,68</t>
+          <t>-21,51; 6,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 30,3</t>
+          <t>-3,75; 30,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 26,26</t>
+          <t>-7,94; 25,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 0,39</t>
+          <t>-16,49; 4,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 13,19</t>
+          <t>-33,53; 12,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 75,73</t>
+          <t>-5,19; 83,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 52,91</t>
+          <t>-11,38; 50,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 0,51</t>
+          <t>-19,95; 6,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-2,16%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,65</t>
+          <t>-0,25; 15,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,13</t>
+          <t>1,2; 18,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 26,24</t>
+          <t>8,58; 25,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 7,81</t>
+          <t>-1,52; 12,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 39,4</t>
+          <t>-0,4; 39,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 45,6</t>
+          <t>2,74; 44,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,68; 65,5</t>
+          <t>18,79; 64,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 13,13</t>
+          <t>-2,22; 23,04</t>
         </is>
       </c>
     </row>
